--- a/test/excel/parts/struct-held/copy-fill.xlsx
+++ b/test/excel/parts/struct-held/copy-fill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11004"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11027"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/user/Library/Containers/com.microsoft.Excel/Data/tmp/fparts-11941/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mike/Library/Containers/com.microsoft.Excel/Data/tmp/fsave-29694/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{007A0014-79AC-8245-AC7C-BE63B982D32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7039984-B2F0-AC4C-B9A7-5BFF079F7206}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="21680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
     <author>Ann</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{B0A73CC1-45B3-E149-AC51-0C130448F9C9}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{A818AE0A-1F87-0545-8D25-D5F32EC09D99}">
       <text>
         <r>
           <rPr>
@@ -48,7 +48,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{20BD2C1E-4697-2C4E-A9FF-27C5396EB178}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{277D7AC4-9156-9A4C-BA24-2557359E426A}">
       <text>
         <r>
           <rPr>
@@ -70,7 +70,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{D36B247A-1028-AD44-8B8F-E36F81B17738}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{D02089BD-F917-ED4B-AEC8-1F5A01B1E706}">
       <text>
         <r>
           <rPr>
@@ -577,9 +577,9 @@
     <hyperlink ref="B3" r:id="rId1" tooltip="B3" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" location="S!A1" display="to A1" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
     <hyperlink ref="D6" location="'T'!A1" display="to T" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="F2" r:id="rId2" tooltip="B3" xr:uid="{FF38D445-16A8-D249-8CFF-D06D1BFE460D}"/>
-    <hyperlink ref="F4" r:id="rId3" tooltip="B3" xr:uid="{FCED6400-7737-A54C-9915-2C6FB9460B66}"/>
-    <hyperlink ref="F6" r:id="rId4" tooltip="B3" xr:uid="{B7AC6BE3-C884-2B44-890B-7F696084D6DB}"/>
+    <hyperlink ref="F2" r:id="rId2" tooltip="B3" xr:uid="{8FC7B105-A08E-AE4E-AB19-23E281418A87}"/>
+    <hyperlink ref="F4" r:id="rId3" tooltip="B3" xr:uid="{8672D669-B216-8749-8245-363762A206E6}"/>
+    <hyperlink ref="F6" r:id="rId4" tooltip="B3" xr:uid="{4A9C0A09-D2C6-0547-B609-8333AE5BADD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId5"/>
